--- a/math/06函数.xlsx
+++ b/math/06函数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9024486-ED25-3C48-9479-56F73A1BC435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E837F6CF-4AA5-F04E-901A-68639E0E5DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{45CB8B69-B965-4946-AA4C-E59F130AED00}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
   <si>
     <t>1、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -278,6 +278,70 @@
   </si>
   <si>
     <t>解方程求出k，再回代解析式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一象限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右上x&gt;0,y&gt;0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二象限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左上x&lt;0,y&gt;0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三象限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左下x&lt;0,y&lt;0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第四象限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右下x&gt;0,y&lt;0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘦狗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>明星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现金牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二次函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>概率与统计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不等式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -680,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095FA0BA-76A8-1646-A878-83BD9210923F}">
-  <dimension ref="B1:J69"/>
+  <dimension ref="B1:K72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="2"/>
@@ -720,10 +784,18 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="J6" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J7" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C9" s="2" t="s">
@@ -886,7 +958,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:11" x14ac:dyDescent="0.15">
       <c r="C50" s="2" t="s">
         <v>43</v>
       </c>
@@ -894,17 +966,17 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:11" x14ac:dyDescent="0.15">
       <c r="D51" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:11" x14ac:dyDescent="0.15">
       <c r="D52" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:11" x14ac:dyDescent="0.15">
       <c r="D53" s="2" t="s">
         <v>47</v>
       </c>
@@ -912,47 +984,85 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:11" x14ac:dyDescent="0.15">
       <c r="C55" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:11" x14ac:dyDescent="0.15">
       <c r="C56" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:11" x14ac:dyDescent="0.15">
       <c r="C58" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="59" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="I58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="3:11" x14ac:dyDescent="0.15">
       <c r="C59" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="60" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="I59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" spans="3:11" x14ac:dyDescent="0.15">
       <c r="C60" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="62" spans="3:5" x14ac:dyDescent="0.15">
+      <c r="I60" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="3:11" x14ac:dyDescent="0.15">
+      <c r="I61" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="3:11" x14ac:dyDescent="0.15">
       <c r="C62" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="64" spans="3:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:11" x14ac:dyDescent="0.15">
       <c r="C64" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.15">
       <c r="C65" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.15">
       <c r="C67" s="2" t="s">
         <v>56</v>
       </c>
@@ -960,14 +1070,22 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.15">
       <c r="D68" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.15">
       <c r="D69" s="2" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="B72" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/math/06函数.xlsx
+++ b/math/06函数.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E837F6CF-4AA5-F04E-901A-68639E0E5DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD13E41A-85FF-C443-A122-6F5CE9D1D633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{45CB8B69-B965-4946-AA4C-E59F130AED00}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="137">
   <si>
     <t>1、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -342,6 +342,250 @@
   </si>
   <si>
     <t>不等式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y=ax2+bx+c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a、b、c为常数，且a&lt;&gt;0的函数，是二次函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x是自变量，y是因变量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自变量最高次数为2，且二次项系数a不能为0（否则退化为一次函数或常数函数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三种表达式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接体现二次项系数a、一次项系数b和常数项c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当x=0时，y=c，即图像与y轴交叉点为(0,c)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般式 y=ax2+bx+c(a&lt;&gt;0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顶点项 y=a(x-h)2+k(a&lt;&gt;0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其中(h,k)是二次函数图像的顶点坐标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优点：可直接看出顶点位置，便于分析函数的最值和对称性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交点项（两根式）y=a(x-x1)(x-x2)(a&lt;&gt;0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其中x1、x2是二次函数图像与x轴交点的横坐标（即对应一元二次方程ax2+bx+c=0的两个根）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前提：函数图像与x轴有交点（即判别式Δ=b2-4ac&gt;=0）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二次函数的图像是一条抛物线，其性质与系数a、b、c密切相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.开口方向与开口大小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由a决定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若a&gt;0，抛物线开口向上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若a&lt;0，抛物线开口向下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>|a|越大，抛物线开口越窄；|a|越小，开口越宽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.顶点与最值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顶点坐标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般式中，顶点坐标为x=-b/2a，代入一般式可求纵坐标，即顶点为(-b/2a,4ac-b2/4a)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顶点式中，直接为(h,k)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若a&gt;0，抛物线有最小值，当x=h时，ymin=k</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若a&lt;0，抛物线有最大值，当x=h时，ymax=k</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y=2x2+3x+4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先a&gt;0，说明开口朝上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顶点位置(h,k)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>h=-b/2a=-3/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>k=4ac-b2/4a=4*2*4-9/8=23/8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.对称性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抛物线是轴对称图形，对称轴是过顶点且垂直于x轴的直线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般式中，对称轴为x=-b/2a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顶点式中，对称轴为x=h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对称轴两侧的函数单调性相反</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当a&gt;0时，对称轴左侧(x&lt;h)函数单调递减，右侧(x&gt;h)单调递增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当a&lt;0时，对称轴左侧(x&lt;h)函数单调递增，右侧(x&gt;h)单调递减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.与坐标轴的交点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与y轴交点：恒为(0,c)代入x=0求解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与x轴交点：解方程ax2+bx+c=0，判别式Δ=b2-4ac决定交点个数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δ&gt;0：2个不同交点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δ=0：1个交点（顶点在x轴上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Δ&lt;0：无交点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>函数的定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个变量（自变量）的取值确定后，另一个变量（因变量）的取值也被唯一确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这种变量间的“唯一对应”关系就是函数 y=f(x)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定义域A：自变量x的取值范围（必须是非空数集）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应关系f：将x映射到y的规则（如公式、图像、表格等）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>值域：所有对应的y组成的集合（是B的子集）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>函数的定义域：自变量x的取值范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.分式：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分母&lt;&gt;0（如y=1/x-1中，x&lt;&gt;1）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.偶次根式：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被开方数&gt;=0（如y=√x-2中，x&gt;=2）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.对数函数：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真数&gt;0，底数&gt;0且&lt;&gt;1（如y=log2(x+1)中，x&gt;-1）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.实际问题：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需符合实际意义（如时间、长度不能为负）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -744,23 +988,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095FA0BA-76A8-1646-A878-83BD9210923F}">
-  <dimension ref="B1:K72"/>
+  <dimension ref="B1:M127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -770,52 +1014,83 @@
       <c r="J3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="L3" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="L4" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="L5" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="J6" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="L7" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="L8" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="L9" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="L11" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="L12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
@@ -825,21 +1100,39 @@
       <c r="F13" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="L13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="L14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.15">
@@ -1086,6 +1379,233 @@
       </c>
       <c r="C72" s="1" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="C74" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="C76" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="C77" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="C78" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.15">
+      <c r="C80" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C82" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C83" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C84" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C86" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C87" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C88" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C90" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C91" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C92" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C94" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.15">
+      <c r="C95" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C97" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C98" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D99" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C100" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C102" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C103" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D104" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C105" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D106" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C108" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D109" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D110" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="111" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D111" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="112" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D112" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="114" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C114" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="115" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C115" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D116" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="117" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D117" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="118" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C118" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D119" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="120" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="D120" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="122" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C122" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="123" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C123" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="124" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C124" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="125" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C125" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="126" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C126" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="127" spans="3:4" x14ac:dyDescent="0.15">
+      <c r="C127" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
